--- a/F3M_Auditoria_Interna_assessment_ready_AI_v0.xlsx
+++ b/F3M_Auditoria_Interna_assessment_ready_AI_v0.xlsx
@@ -131,10 +131,10 @@
     <t>Planificación integrada con ERM, compliance, controles internos, cambios del negocio y señales de riesgo, con revisión dinámica del plan.</t>
   </si>
   <si>
-    <t>Planificación continua y predictiva, con AI para monitorizar cambios internos/externos, anticipar áreas de riesgo y recomendar ajustes al plan de auditoría.</t>
-  </si>
-  <si>
-    <t>Predictive compliance monitoring; AI-powered risk management and regulatory compliance; Global policy tracking</t>
+    <t>Planificación continua y predictiva, con IA para monitorizar cambios internos/externos, anticipar áreas de riesgo y recomendar ajustes al plan de auditoría.</t>
+  </si>
+  <si>
+    <t>Monitorización predictiva del cumplimiento; Gestión de riesgos y cumplimiento regulatorio impulsados por IA; Seguimiento de políticas globales</t>
   </si>
   <si>
     <t>¿Existe un universo auditable formal y actualizado?
@@ -167,10 +167,10 @@
     <t>Ejecución integrada con analytics, controles automatizados, priorización por riesgo y trazabilidad completa de pruebas y hallazgos.</t>
   </si>
   <si>
-    <t>Auditoría AI-enabled con pruebas continuas, selección inteligente de muestras, análisis de poblaciones completas y recomendaciones sobre foco de testing.</t>
-  </si>
-  <si>
-    <t>AI-supported regulatory examinations and inspections; AI-powered risk management and regulatory compliance; Reconcile account balances at transaction level to invoices, purchase orders and bank statements</t>
+    <t>Auditoría basada en IA con pruebas continuas, selección inteligente de muestras, análisis de poblaciones completas y recomendaciones sobre foco de testing.</t>
+  </si>
+  <si>
+    <t>Exámenes e inspecciones regulatorias asistidos por IA; Gestión de riesgos y cumplimiento regulatorio impulsados por IA; Conciliación de saldos contables a nivel de transacción con facturas, pedidos de compra y extractos bancarios</t>
   </si>
   <si>
     <t>¿Existe metodología estándar de auditoría?
@@ -203,10 +203,10 @@
     <t>Reporting integrado con dashboards, tendencias de riesgos, severidad, owners, evolución de hallazgos y mensajes ejecutivos.</t>
   </si>
   <si>
-    <t>Generación asistida de informes de assurance con AI, síntesis de evidencias, detección de inconsistencias y narrativa ejecutiva orientada a decisiones.</t>
-  </si>
-  <si>
-    <t>Research-based report generation / KYC; Smarter intelligence; Insights for all</t>
+    <t>Generación asistida de informes de assurance con IA, síntesis de evidencias, detección de inconsistencias y narrativa ejecutiva orientada a decisiones.</t>
+  </si>
+  <si>
+    <t>Generación de informes de investigación / KYC; Inteligencia más avanzada; Análisis accesibles para toda la organización</t>
   </si>
   <si>
     <t>¿Los informes tienen estructura y ratings homogéneos?
@@ -239,10 +239,10 @@
     <t>Gestión integrada de remediación con priorización por riesgo, alertas, escalados, validación de efectividad y reporting a comités.</t>
   </si>
   <si>
-    <t>AI prioriza acciones, anticipa retrasos, recomienda escalados y detecta patrones recurrentes de control para prevenir reincidencias.</t>
-  </si>
-  <si>
-    <t>Predictive compliance monitoring; Proactive defect resolution recommendations; AI-powered risk management and regulatory compliance</t>
+    <t>IA prioriza acciones, anticipa retrasos, recomienda escalados y detecta patrones recurrentes de control para prevenir reincidencias.</t>
+  </si>
+  <si>
+    <t>Monitorización predictiva del cumplimiento; Recomendaciones proactivas para la resolución de incidencias; Gestión de riesgos y cumplimiento regulatorio impulsados por IA</t>
   </si>
   <si>
     <t>¿Cada hallazgo tiene owner, acción y fecha?
@@ -278,10 +278,10 @@
     <t>Advisory integrado en iniciativas estratégicas y de transformación, con priorización por riesgo, coordinación con segunda línea y medición de valor aportado.</t>
   </si>
   <si>
-    <t>Modelo proactivo de advisory basado en señales de riesgo y AI, que recomienda focos de asesoramiento y aporta insights preventivos sin comprometer independencia.</t>
-  </si>
-  <si>
-    <t>AI-powered risk management and regulatory compliance; Smarter intelligence; Insights for all</t>
+    <t>Modelo proactivo de advisory basado en señales de riesgo y IA, que recomienda focos de asesoramiento y aporta insights preventivos sin comprometer independencia.</t>
+  </si>
+  <si>
+    <t>Gestión de riesgos y cumplimiento regulatorio impulsados por IA; Inteligencia más avanzada; Análisis accesibles para toda la organización</t>
   </si>
   <si>
     <t>¿Está definido el rol de advisory?
@@ -314,10 +314,10 @@
     <t>Advisory integrado en programas críticos, con checkpoints, criterios de control by design, métricas de riesgo y coordinación con PMO/segunda línea.</t>
   </si>
   <si>
-    <t>AI apoya la identificación temprana de riesgos de transformación, brechas de control, cambios regulatorios y recomendaciones de diseño preventivo.</t>
-  </si>
-  <si>
-    <t>Code assistant for digital transformation; AI-driven vulnerability management; Financial rules and regulations interpretations</t>
+    <t>IA apoya la identificación temprana de riesgos de transformación, brechas de control, cambios regulatorios y recomendaciones de diseño preventivo.</t>
+  </si>
+  <si>
+    <t>Asistente de código para la transformación digital; Gestión de vulnerabilidades basada en IA; Interpretación de normas y regulación financiera</t>
   </si>
   <si>
     <t>¿Auditoría participa en proyectos desde diseño?
@@ -350,10 +350,10 @@
     <t>Challenge integrado en decisiones críticas, con análisis de escenarios, impactos, apetito de riesgo y seguimiento de recomendaciones.</t>
   </si>
   <si>
-    <t>Decision support AI-enabled con búsqueda de evidencias, síntesis multifuente, escenarios de riesgo y recomendaciones de challenge para comités.</t>
-  </si>
-  <si>
-    <t>Smarter intelligence; Enterprise-wide data search and access; Global policy tracking</t>
+    <t>Decision support basado en IA con búsqueda de evidencias, síntesis multifuente, escenarios de riesgo y recomendaciones de challenge para comités.</t>
+  </si>
+  <si>
+    <t>Inteligencia más avanzada; Búsqueda y acceso a datos en toda la compañía; Seguimiento de políticas globales</t>
   </si>
   <si>
     <t>¿Auditoría participa en foros de decisión clave?
@@ -386,10 +386,10 @@
     <t>Gestión integrada de conocimiento con comunidades, analytics de hallazgos, formación por riesgo y medición de adopción.</t>
   </si>
   <si>
-    <t>AI knowledge assistant que permite consultar políticas, controles, hallazgos, benchmarks y recomendaciones contextualizadas para mejorar la cultura de control.</t>
-  </si>
-  <si>
-    <t>AI-powered archive access and extraction; Enterprise-wide data search and access; Data access for all</t>
+    <t>Asistente de conocimiento con IA que permite consultar políticas, controles, hallazgos, benchmarks y recomendaciones contextualizadas para mejorar la cultura de control.</t>
+  </si>
+  <si>
+    <t>Acceso y extracción documental impulsados por IA; Búsqueda y acceso a datos en toda la compañía; Acceso a datos para toda la organización</t>
   </si>
   <si>
     <t>¿Existen guías y repositorio de buenas prácticas?
@@ -425,10 +425,10 @@
     <t>Monitorización integrada con datos transaccionales, controles automatizados, workflows de excepción y reporting por riesgo.</t>
   </si>
   <si>
-    <t>Continuous auditing AI-enabled con detección de desviaciones, priorización dinámica y alertas tempranas sobre riesgos emergentes.</t>
-  </si>
-  <si>
-    <t>Predictive compliance monitoring; AI-powered risk management and regulatory compliance; Automated regulatory compliance</t>
+    <t>Continuous auditing basado en IA con detección de desviaciones, priorización dinámica y alertas tempranas sobre riesgos emergentes.</t>
+  </si>
+  <si>
+    <t>Monitorización predictiva del cumplimiento; Gestión de riesgos y cumplimiento regulatorio impulsados por IA; Cumplimiento regulatorio automatizado</t>
   </si>
   <si>
     <t>¿Existen KRIs/KCIs definidos?
@@ -461,10 +461,10 @@
     <t>Analítica avanzada y monitorización recurrente sobre poblaciones completas, priorizando casos por materialidad, riesgo e impacto.</t>
   </si>
   <si>
-    <t>Modelos AI de fraude/anomalías en tiempo real, con scoring, explicación, aprendizaje continuo y workflow de investigación.</t>
-  </si>
-  <si>
-    <t>Monitor potentially suspect or fraudulent journal entries in real time; Proactive detection of fraudulent activities; Identify unusual entries recorded during the close period</t>
+    <t>Modelos IA de fraude/anomalías en tiempo real, con scoring, explicación, aprendizaje continuo y workflow de investigación.</t>
+  </si>
+  <si>
+    <t>Monitorización en tiempo real de asientos potencialmente sospechosos o fraudulentos; Detección proactiva de actividades fraudulentas; Identificación de asientos inusuales registrados durante el periodo de cierre</t>
   </si>
   <si>
     <t>¿Se detectan anomalías en datos financieros?
@@ -497,10 +497,10 @@
     <t>Modelos predictivos recurrentes conectados con datos internos/externos, apetito de riesgo, KRIs y priorización de auditoría.</t>
   </si>
   <si>
-    <t>AI anticipa cambios de exposición, simula escenarios de riesgo y recomienda acciones preventivas, auditorías o revisiones focalizadas.</t>
-  </si>
-  <si>
-    <t>Synthetic data generation; Predictive compliance monitoring; AI-driven vulnerability management</t>
+    <t>IA anticipa cambios de exposición, simula escenarios de riesgo y recomienda acciones preventivas, auditorías o revisiones focalizadas.</t>
+  </si>
+  <si>
+    <t>Generación de datos sintéticos; Monitorización predictiva del cumplimiento; Gestión de vulnerabilidades basada en IA</t>
   </si>
   <si>
     <t>¿Se anticipan cambios de exposición?
@@ -533,10 +533,10 @@
     <t>Gestión integrada de incidentes con workflow, priorización por riesgo, análisis de tendencias, remediación y reporting a comités.</t>
   </si>
   <si>
-    <t>AI apoya la investigación con análisis multifuente, clustering de incidentes, recomendaciones de respuesta y aprendizaje preventivo sobre causas recurrentes.</t>
-  </si>
-  <si>
-    <t>Autonomous warranty adjudication; AI-driven visual inspection for particulate matter; Proactive defect resolution recommendations</t>
+    <t>IA apoya la investigación con análisis multifuente, clustering de incidentes, recomendaciones de respuesta y aprendizaje preventivo sobre causas recurrentes.</t>
+  </si>
+  <si>
+    <t>Resolución autónoma de garantías; Inspección visual de partículas basada en IA; Recomendaciones proactivas para la resolución de incidencias</t>
   </si>
   <si>
     <t>¿Existe proceso formal de investigación?

--- a/F3M_Auditoria_Interna_assessment_ready_AI_v0.xlsx
+++ b/F3M_Auditoria_Interna_assessment_ready_AI_v0.xlsx
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="223">
   <si>
     <t>Capacidad</t>
   </si>
@@ -724,6 +724,45 @@
   </si>
   <si>
     <t>Evaluar situación actual, sustentar el score con evidencias, separar las tres palancas, validar resultados con los responsables del dominio y no sobrevalorar tecnología sin proceso/adopción madura.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitorización predictiva del cumplimiento; Vigilancia continua de riesgo y cumplimiento; Seguimiento de políticas y regulación global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Apoyo a exámenes e inspecciones regulatorias; Vigilancia continua de riesgo y cumplimiento; Conciliación a nivel de transacción; Generación de casos de prueba de control</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Informes de investigación y KYC; Síntesis multifuente para informes de análisis; Consulta del dato en lenguaje natural; Borrador de informe de auditoría</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitorización predictiva del cumplimiento; Recomendaciones de resolución de incidencias; Vigilancia continua de riesgo y cumplimiento</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vigilancia continua de riesgo y cumplimiento; Síntesis multifuente para informes de análisis; Consulta del dato en lenguaje natural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Asistente de código para la transformación; Gestión de vulnerabilidades con IA; Interpretación de normativa financiera</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Síntesis multifuente para informes de análisis; Consulta del dato en lenguaje natural; Seguimiento de políticas y regulación global</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acceso y extracción documental; Consulta del dato en lenguaje natural</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitorización predictiva del cumplimiento; Vigilancia continua de riesgo y cumplimiento; Cumplimiento regulatorio automatizado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vigilancia en tiempo real de asientos sospechosos; Detección proactiva de fraude; Detección de asientos inusuales en el cierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Generación de datos sintéticos; Monitorización predictiva del cumplimiento; Gestión de vulnerabilidades con IA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recomendaciones de resolución de incidencias; Detección proactiva de fraude</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Resolución autónoma de garantías; Recomendaciones de resolución de incidencias; Detección proactiva de fraude</t>
   </si>
 </sst>
 </file>
@@ -1470,7 +1509,7 @@
         <v>27</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="J2" s="2"/>
       <c r="K2" s="2"/>
@@ -1528,7 +1567,7 @@
         <v>38</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -1586,7 +1625,7 @@
         <v>49</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
@@ -1644,7 +1683,7 @@
         <v>60</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
@@ -1702,7 +1741,7 @@
         <v>72</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
@@ -1760,7 +1799,7 @@
         <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1818,7 +1857,7 @@
         <v>94</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1876,7 +1915,7 @@
         <v>105</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1934,7 +1973,7 @@
         <v>117</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1992,7 +2031,7 @@
         <v>128</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2050,7 +2089,7 @@
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2108,7 +2147,7 @@
         <v>150</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2852,7 +2891,7 @@
         <v>31</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="G2" s="2" t="str">
         <f t="shared" ref="G2:G13" si="0">IF(C2="","",IF(C2&gt;=3,"Oleada 1",IF(C2=2,"Oleada 2",IF(C2=1,"Oleada 3",""))))</f>
@@ -2883,7 +2922,7 @@
         <v>42</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="G3" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2914,7 +2953,7 @@
         <v>53</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="G4" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2945,7 +2984,7 @@
         <v>64</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="G5" s="2" t="str">
         <f t="shared" si="0"/>
@@ -2976,7 +3015,7 @@
         <v>76</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="G6" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3007,7 +3046,7 @@
         <v>87</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="G7" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3038,7 +3077,7 @@
         <v>98</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="G8" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3069,7 +3108,7 @@
         <v>109</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="G9" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3100,7 +3139,7 @@
         <v>121</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="G10" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3131,7 +3170,7 @@
         <v>132</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="G11" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3162,7 +3201,7 @@
         <v>143</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="G12" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3193,7 +3232,7 @@
         <v>154</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="G13" s="2" t="str">
         <f t="shared" si="0"/>
@@ -3253,7 +3292,7 @@
         <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>28</v>
+        <v>210</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>27</v>
@@ -3270,7 +3309,7 @@
         <v>32</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>39</v>
+        <v>211</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>38</v>
@@ -3287,7 +3326,7 @@
         <v>43</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>50</v>
+        <v>212</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>49</v>
@@ -3304,7 +3343,7 @@
         <v>54</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>60</v>
@@ -3321,7 +3360,7 @@
         <v>66</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>73</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>72</v>
@@ -3338,7 +3377,7 @@
         <v>77</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>83</v>
@@ -3355,7 +3394,7 @@
         <v>88</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>95</v>
+        <v>216</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>94</v>
@@ -3372,7 +3411,7 @@
         <v>99</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>217</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>105</v>
@@ -3389,7 +3428,7 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>218</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>117</v>
@@ -3406,7 +3445,7 @@
         <v>122</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>128</v>
@@ -3423,7 +3462,7 @@
         <v>133</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>139</v>
@@ -3440,7 +3479,7 @@
         <v>144</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>151</v>
+        <v>221</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>150</v>

--- a/F3M_Auditoria_Interna_assessment_ready_AI_v0.xlsx
+++ b/F3M_Auditoria_Interna_assessment_ready_AI_v0.xlsx
@@ -167,7 +167,7 @@
     <t>Ejecución integrada con analytics, controles automatizados, priorización por riesgo y trazabilidad completa de pruebas y hallazgos.</t>
   </si>
   <si>
-    <t>Auditoría basada en IA con pruebas continuas, selección inteligente de muestras, análisis de poblaciones completas y recomendaciones sobre foco de testing.</t>
+    <t>Auditoría basada en IA con pruebas continuas, selección inteligente de muestras, análisis de poblaciones completas y recomendaciones sobre foco de pruebas.</t>
   </si>
   <si>
     <t>Exámenes e inspecciones regulatorias asistidos por IA; Gestión de riesgos y cumplimiento regulatorio impulsados por IA; Conciliación de saldos contables a nivel de transacción con facturas, pedidos de compra y extractos bancarios</t>
@@ -203,7 +203,7 @@
     <t>Reporting integrado con dashboards, tendencias de riesgos, severidad, owners, evolución de hallazgos y mensajes ejecutivos.</t>
   </si>
   <si>
-    <t>Generación asistida de informes de assurance con IA, síntesis de evidencias, detección de inconsistencias y narrativa ejecutiva orientada a decisiones.</t>
+    <t>Generación asistida de informes de aseguramiento con IA, síntesis de evidencias, detección de inconsistencias y narrativa ejecutiva orientada a decisiones.</t>
   </si>
   <si>
     <t>Generación de informes de investigación / KYC; Inteligencia más avanzada; Análisis accesibles para toda la organización</t>
@@ -278,7 +278,7 @@
     <t>Advisory integrado en iniciativas estratégicas y de transformación, con priorización por riesgo, coordinación con segunda línea y medición de valor aportado.</t>
   </si>
   <si>
-    <t>Modelo proactivo de advisory basado en señales de riesgo y IA, que recomienda focos de asesoramiento y aporta insights preventivos sin comprometer independencia.</t>
+    <t>Modelo proactivo de asesoramiento basado en señales de riesgo e IA, que recomienda dónde asesorar y aporta conclusiones preventivas sin comprometer la independencia.</t>
   </si>
   <si>
     <t>Gestión de riesgos y cumplimiento regulatorio impulsados por IA; Inteligencia más avanzada; Análisis accesibles para toda la organización</t>
@@ -350,7 +350,7 @@
     <t>Challenge integrado en decisiones críticas, con análisis de escenarios, impactos, apetito de riesgo y seguimiento de recomendaciones.</t>
   </si>
   <si>
-    <t>Decision support basado en IA con búsqueda de evidencias, síntesis multifuente, escenarios de riesgo y recomendaciones de challenge para comités.</t>
+    <t>Apoyo a la decisión basado en IA, con búsqueda de evidencias, síntesis multifuente, escenarios de riesgo y propuestas de contraste crítico para los comités.</t>
   </si>
   <si>
     <t>Inteligencia más avanzada; Búsqueda y acceso a datos en toda la compañía; Seguimiento de políticas globales</t>
@@ -425,7 +425,7 @@
     <t>Monitorización integrada con datos transaccionales, controles automatizados, workflows de excepción y reporting por riesgo.</t>
   </si>
   <si>
-    <t>Continuous auditing basado en IA con detección de desviaciones, priorización dinámica y alertas tempranas sobre riesgos emergentes.</t>
+    <t>Auditoría continua basada en IA, con detección de desviaciones, priorización dinámica y alertas tempranas sobre riesgos emergentes.</t>
   </si>
   <si>
     <t>Monitorización predictiva del cumplimiento; Gestión de riesgos y cumplimiento regulatorio impulsados por IA; Cumplimiento regulatorio automatizado</t>
@@ -461,7 +461,7 @@
     <t>Analítica avanzada y monitorización recurrente sobre poblaciones completas, priorizando casos por materialidad, riesgo e impacto.</t>
   </si>
   <si>
-    <t>Modelos IA de fraude/anomalías en tiempo real, con scoring, explicación, aprendizaje continuo y workflow de investigación.</t>
+    <t>Modelos IA de fraude/anomalías en tiempo real, con puntuación, explicación, aprendizaje continuo y flujo de trabajo de investigación.</t>
   </si>
   <si>
     <t>Monitorización en tiempo real de asientos potencialmente sospechosos o fraudulentos; Detección proactiva de actividades fraudulentas; Identificación de asientos inusuales registrados durante el periodo de cierre</t>
@@ -533,7 +533,7 @@
     <t>Gestión integrada de incidentes con workflow, priorización por riesgo, análisis de tendencias, remediación y reporting a comités.</t>
   </si>
   <si>
-    <t>IA apoya la investigación con análisis multifuente, clustering de incidentes, recomendaciones de respuesta y aprendizaje preventivo sobre causas recurrentes.</t>
+    <t>IA apoya la investigación con análisis multifuente, agrupación de incidentes, recomendaciones de respuesta y aprendizaje preventivo sobre causas recurrentes.</t>
   </si>
   <si>
     <t>Resolución autónoma de garantías; Inspección visual de partículas basada en IA; Recomendaciones proactivas para la resolución de incidencias</t>

--- a/F3M_Auditoria_Interna_assessment_ready_AI_v0.xlsx
+++ b/F3M_Auditoria_Interna_assessment_ready_AI_v0.xlsx
@@ -182,7 +182,7 @@
     <t>Programas de auditoría; matrices riesgo-control; papeles de trabajo; evidencias de testing; revisiones de calidad; muestras.</t>
   </si>
   <si>
-    <t>Estandarizar metodología de auditoría y testing con matrices riesgo-control, evidencias, analytics y trazabilidad de ejecución.</t>
+    <t>Estandarizar metodología de auditoría y pruebas con matrices riesgo-control, evidencias, analítica de datos y trazabilidad de ejecución.</t>
   </si>
   <si>
     <t>1.3 Calidad, trazabilidad y reporting de assurance</t>
@@ -218,7 +218,7 @@
     <t>Informes de auditoría; ratings; papeles de trabajo; evidencias; revisiones de calidad; dashboards de assurance.</t>
   </si>
   <si>
-    <t>Rediseñar reporting de assurance con estructura común, ratings, causa-raíz, trazabilidad de evidencia y dashboard ejecutivo.</t>
+    <t>Rediseñar los informes de aseguramiento con estructura común, calificaciones, causa-raíz, trazabilidad de evidencia y cuadro de mando ejecutivo.</t>
   </si>
   <si>
     <t>1.4 Seguimiento de hallazgos y remediación</t>
@@ -254,7 +254,7 @@
     <t>Tracker de hallazgos; planes de acción; evidencias de cierre; actas de comité; reportes de aging; validaciones.</t>
   </si>
   <si>
-    <t>Implantar modelo de remediación con workflow, alertas, evidencias, validación de efectividad, escalado y análisis de recurrencias.</t>
+    <t>Implantar modelo de remediación con flujo de trabajo, alertas, evidencias, validación de efectividad, escalado y análisis de recurrencias.</t>
   </si>
   <si>
     <t>Asesoramiento de riesgos</t>
@@ -293,7 +293,7 @@
     <t>Modelo de advisory; criterios de independencia; portfolio de advisory; actas de steering; feedback de stakeholders; entregables.</t>
   </si>
   <si>
-    <t>Definir modelo de advisory de Auditoría Interna con criterios de independencia, priorización por riesgo, entregables y métricas de valor.</t>
+    <t>Definir modelo de asesoramiento de Auditoría Interna con criterios de independencia, priorización por riesgo, entregables y métricas de valor.</t>
   </si>
   <si>
     <t>2.2 Asesoramiento en transformación, procesos y controles</t>
@@ -329,7 +329,7 @@
     <t>Comités de proyecto; risk/control design reviews; matrices SoD; recomendaciones; checkpoints; documentación de transformación.</t>
   </si>
   <si>
-    <t>Crear metodología de advisory en transformación con control by design, checkpoints, criterios de riesgo y coordinación con segunda línea/PMO.</t>
+    <t>Crear metodología de asesoramiento en transformación con control desde el diseño, puntos de control, criterios de riesgo y coordinación con segunda línea y PMO.</t>
   </si>
   <si>
     <t>2.3 Challenge independiente y soporte a decisiones de riesgo</t>
@@ -365,7 +365,7 @@
     <t>Actas de comité; recomendaciones de Auditoría; análisis de riesgos; escenarios; documentación de decisiones; seguimiento.</t>
   </si>
   <si>
-    <t>Formalizar modelo de challenge independiente con criterios, evidencias, escenarios, recomendaciones y seguimiento de decisiones de riesgo.</t>
+    <t>Formalizar modelo de contraste independiente con criterios, evidencias, escenarios, recomendaciones y seguimiento de decisiones de riesgo.</t>
   </si>
   <si>
     <t>2.4 Gestión de conocimiento, capacidades y cultura de control</t>
@@ -401,7 +401,7 @@
     <t>Repositorio; guías de control; planes de formación; comunicaciones; encuestas; analytics de hallazgos; lecciones aprendidas.</t>
   </si>
   <si>
-    <t>Implantar repositorio y programa de cultura de control con guías, formación por riesgo, lecciones aprendidas y knowledge assistant.</t>
+    <t>Implantar repositorio y programa de cultura de control con guías, formación por riesgo, lecciones aprendidas y asistente de conocimiento.</t>
   </si>
   <si>
     <t>Detección de riesgos y previsión</t>
@@ -440,7 +440,7 @@
     <t>Mapa KRIs/KCIs; dashboards; umbrales; logs de excepción; controles automatizados; workflows; actas de seguimiento.</t>
   </si>
   <si>
-    <t>Diseñar modelo de continuous auditing con KRIs/KCIs, datos transaccionales, alertas, workflows y priorización por riesgo.</t>
+    <t>Diseñar modelo de auditoría continua con KRIs y KCIs, datos transaccionales, alertas, flujos de trabajo y priorización por riesgo.</t>
   </si>
   <si>
     <t>3.2 Detección de fraude, anomalías y operaciones sospechosas</t>
@@ -476,7 +476,7 @@
     <t>Alertas de fraude; reglas de detección; modelos analíticos; casos investigados; logs de excepciones; informes de investigación.</t>
   </si>
   <si>
-    <t>Implantar monitor de fraude y anomalías con reglas, modelos predictivos, scoring, explicación y workflow de investigación.</t>
+    <t>Implantar monitor de fraude y anomalías con reglas, modelos predictivos, puntuación de riesgo, explicación y flujo de investigación.</t>
   </si>
   <si>
     <t>3.3 Modelos predictivos de riesgo y escenarios de exposición</t>
@@ -548,7 +548,7 @@
     <t>Registros de incidentes; informes de investigación; evidencias; causa-raíz; planes de remediación; reportes de tendencia.</t>
   </si>
   <si>
-    <t>Formalizar proceso de investigación y respuesta con taxonomy de incidentes, workflow, causa-raíz, acciones y aprendizaje preventivo.</t>
+    <t>Formalizar proceso de investigación y respuesta con taxonomía de incidentes, flujo de trabajo, causa-raíz, acciones y aprendizaje preventivo.</t>
   </si>
   <si>
     <t>Score global dominio</t>
